--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N74_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N74_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.45895092073316</v>
+        <v>4.299579524619138</v>
       </c>
       <c r="D2" t="n">
-        <v>27.02823027092374</v>
+        <v>4.392087419025107</v>
       </c>
       <c r="E2" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F2" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>10.04987666100115</v>
+        <v>1.633104957412687</v>
       </c>
       <c r="D3" t="n">
-        <v>6.628885248582385</v>
+        <v>1.077193852894638</v>
       </c>
       <c r="E3" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F3" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>23.17538116762434</v>
+        <v>3.765999439738955</v>
       </c>
       <c r="D4" t="n">
-        <v>15.61204960539905</v>
+        <v>2.536958060877346</v>
       </c>
       <c r="E4" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F4" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.03568682210732</v>
+        <v>4.55579910859244</v>
       </c>
       <c r="D5" t="n">
-        <v>19.90602923739438</v>
+        <v>3.234729751076587</v>
       </c>
       <c r="E5" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F5" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.27087292448687</v>
+        <v>4.594016850229117</v>
       </c>
       <c r="D6" t="n">
-        <v>14.2126704035519</v>
+        <v>2.309558940577183</v>
       </c>
       <c r="E6" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F6" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>13.20145662405151</v>
+        <v>2.145236701408371</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>1.4625</v>
       </c>
       <c r="E7" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F7" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.6890215900351</v>
+        <v>6.449466008380703</v>
       </c>
       <c r="D8" t="n">
-        <v>22.37428536436838</v>
+        <v>3.635821371709862</v>
       </c>
       <c r="E8" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F8" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>46.25565467319446</v>
+        <v>7.516543884394101</v>
       </c>
       <c r="D9" t="n">
-        <v>22.34390297150433</v>
+        <v>3.630884232869454</v>
       </c>
       <c r="E9" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F9" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.77899698578754</v>
+        <v>5.814087010190476</v>
       </c>
       <c r="D10" t="n">
-        <v>22.83715448561839</v>
+        <v>3.711037603912989</v>
       </c>
       <c r="E10" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F10" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.27916789932242</v>
+        <v>2.970364783639894</v>
       </c>
       <c r="D11" t="n">
-        <v>7.841459270771288</v>
+        <v>1.274237131500334</v>
       </c>
       <c r="E11" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F11" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84370166552743</v>
+        <v>1.762101520648208</v>
       </c>
       <c r="D12" t="n">
-        <v>10.93077694942653</v>
+        <v>1.776251254281811</v>
       </c>
       <c r="E12" t="n">
-        <v>11.342209322804</v>
+        <v>1.84310901495565</v>
       </c>
       <c r="F12" t="n">
-        <v>6.716692574714584</v>
+        <v>1.09146254339112</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
